--- a/Compititor's_Price/Powerlon_Prices/Powerlon_Prices_30-09-2026.xlsx
+++ b/Compititor's_Price/Powerlon_Prices/Powerlon_Prices_30-09-2026.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.insulationshop.co/powerlon_ultraperm_lite_92gsm_breather_membrane_1.0m_x_50m_roll.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_lite_92gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f2aaecd0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.insulationshop.co/powerlon_ultraperm_standard_115gsm_breather_membrane_1.0m_x_25m_roll.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_standard_115gsm_breather_membrane_1.0m_x_25m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f34b2950&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>£28.60</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_standard_115gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f2a9c490&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>£42.14</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_standard_115gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f40e1bd0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>£34.56</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_premium_135gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f34a2dd0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>£50.86</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_premium_135gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f3aa6c10&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.insulationshop.co/powerlon_ultraperm_max_155gsm_breather_membrane_1.0m_x_50m_roll.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_max_155gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f3331f50&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.insulationshop.co/powerlon_ultraperm_max_155gsm_breather_membrane_1.5m_x_50m_roll.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_max_155gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f471e710&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>£87.88</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_supaperm_sp100_housewrap_1.6m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f3dc56d0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.insulationshop.co/powerlon_supaperm_sp100_housewrap_2.7m_x_100m_roll.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_supaperm_sp100_housewrap_2.7m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f3b04890&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>£131.84</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_vcl_250_vapour_control_layer_2m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f30b1150&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>£75.30</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultrablock_200_thermo_reflective_vapour_control_layer_1.6m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f30853d0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.insulationshop.co/powerlon_air_barrier_membrane_1.5m_x_50mm_roll.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_air_barrier_membrane_1.5m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f29c2990&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>£111.79</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_vcl_170_vapour_control_layer_2m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f2fdf0d0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>£238.05</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_uv160sa_uv_resistant_facade_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f3681b10&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Was:£0.00ex VAT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>£209.13</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_uv120_uv_resistant_facade_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f35e8c90&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>£19.68</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_uv_facade_tape_60mm_x_25m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f2f08110&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>£7.66</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerbond_aluminium_fr_vcl_tape_50mm_x_47.5m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f34ea010&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>£7.99</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerbond_double_sided_butyl_tape_2mm_x_15mm_x_24m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f3aa2290&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.insulationshop.co/powerlon_ultraperm_lite_92gsm_breather_membrane_1.5m_x_50m_roll.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_lite_92gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f3b0d610&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>£212.03</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_metalix_metal_roof_separation_layer_1.5m_x_25m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f2d6ce90&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>£175.26</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_supaperm_sp100_housewrap_3.2m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f333fbd0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>£247.60</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_thermaperm_housewrap_1.5m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f2872190&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.insulationshop.co/powerlon_thermaperm_housewrap_2.7m_x_100m_roll.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_thermaperm_housewrap_2.7m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f2effc50&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>£230.23</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultrablock_300_thermo_reflective_vapour_control_layer_2m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f3307410&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>£117.52</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_breathe_fire_retardant_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f3029a50&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>£240.09</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_breathe_fire_retardant_membrane_3m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f3dbae10&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>£102.99</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_block_fire_retardant_membrane_2m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f4729510&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>£147.87</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_block_plus_fire_retardant_membrane_2m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f3266790&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_block_class_a_fire_retardant_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x23821cb1ad0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_block_class_a_fire_retardant_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x141f325ddd0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
